--- a/output/pdf_financials_xlsx/PMI.xlsx
+++ b/output/pdf_financials_xlsx/PMI.xlsx
@@ -1657,10 +1657,10 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.408792</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.5288040000000001</v>
       </c>
     </row>
     <row r="93">
@@ -2756,7 +2756,11 @@
           <t>Reserve 5</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>0.408792</v>
       </c>

--- a/output/pdf_financials_xlsx/PMI.xlsx
+++ b/output/pdf_financials_xlsx/PMI.xlsx
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.015952</v>
       </c>
       <c r="C111" s="1" t="inlineStr">
         <is>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.015952</v>
       </c>
       <c r="C134" s="1" t="inlineStr">
         <is>
@@ -2288,7 +2288,7 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>0</v>
+        <v>-0.015952</v>
       </c>
       <c r="C135" s="1" t="inlineStr">
         <is>
@@ -3208,7 +3208,11 @@
           <t>Purchase of equipment -</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E34" s="5" t="n">
         <v>-0.015952</v>
       </c>
